--- a/SGC-CKN/Excel/4d777394-88bc-4ac1-872d-385d4d9a6ebc_Lô_CT-02_P1-22_D800_31-03-2026.xlsx
+++ b/SGC-CKN/Excel/4d777394-88bc-4ac1-872d-385d4d9a6ebc_Lô_CT-02_P1-22_D800_31-03-2026.xlsx
@@ -328,7 +328,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -338,7 +338,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -1156,19 +1156,19 @@
         <v>28</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.58</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>-4.48</v>
+        <v>-1.18</v>
       </c>
       <c r="H11" s="5">
         <v>0.25</v>
       </c>
       <c r="I11" s="5">
-        <v>3.9</v>
+        <v>1.18</v>
       </c>
       <c r="J11" s="8">
-        <v>15.6</v>
+        <v>4.72</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>29</v>
@@ -1191,19 +1191,19 @@
         <v>32</v>
       </c>
       <c r="F12" s="9">
-        <v>-4.48</v>
+        <v>-1.18</v>
       </c>
       <c r="G12" s="9">
-        <v>-4.98</v>
+        <v>-4.28</v>
       </c>
       <c r="H12" s="9">
         <v>0.33</v>
       </c>
       <c r="I12" s="9">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J12" s="12">
-        <v>1.5</v>
+        <v>9.3</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>29</v>
@@ -1226,7 +1226,7 @@
         <v>35</v>
       </c>
       <c r="F13" s="13">
-        <v>-4.98</v>
+        <v>-4.28</v>
       </c>
       <c r="G13" s="13">
         <v>-7.58</v>
@@ -1235,10 +1235,10 @@
         <v>0.5</v>
       </c>
       <c r="I13" s="13">
-        <v>2.6</v>
-      </c>
-      <c r="J13" s="8">
-        <v>5.2</v>
+        <v>3.3</v>
+      </c>
+      <c r="J13" s="12">
+        <v>6.6</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>29</v>
@@ -1272,7 +1272,7 @@
       <c r="I14" s="16">
         <v>8.8</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="12">
         <v>16</v>
       </c>
       <c r="K14" s="17" t="s">
@@ -1307,7 +1307,7 @@
       <c r="I15" s="19">
         <v>5.2</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="12">
         <v>14.18</v>
       </c>
       <c r="K15" s="20" t="s">
@@ -1342,7 +1342,7 @@
       <c r="I16" s="22">
         <v>4</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J16" s="12">
         <v>11.43</v>
       </c>
       <c r="K16" s="23" t="s">
@@ -1377,7 +1377,7 @@
       <c r="I17" s="25">
         <v>14.22</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="12">
         <v>9.81</v>
       </c>
       <c r="K17" s="26" t="s">
@@ -1404,16 +1404,16 @@
         <v>-39.8</v>
       </c>
       <c r="G18" s="28">
-        <v>-44.42</v>
+        <v>-44.41</v>
       </c>
       <c r="H18" s="28">
         <v>5.4</v>
       </c>
       <c r="I18" s="28">
-        <v>4.62</v>
+        <v>4.61</v>
       </c>
       <c r="J18" s="31">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>29</v>
@@ -1568,19 +1568,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.58</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>-4.48</v>
+        <v>-1.18</v>
       </c>
       <c r="G2" s="5">
         <v>0.25</v>
       </c>
       <c r="H2" s="5">
-        <v>3.9</v>
+        <v>1.18</v>
       </c>
       <c r="I2" s="8">
-        <v>15.6</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1597,19 +1597,19 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-4.48</v>
+        <v>-1.18</v>
       </c>
       <c r="F3" s="9">
-        <v>-4.98</v>
+        <v>-4.28</v>
       </c>
       <c r="G3" s="9">
         <v>0.33</v>
       </c>
       <c r="H3" s="9">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="I3" s="12">
-        <v>1.5</v>
+        <v>9.3</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1626,7 +1626,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="13">
-        <v>-4.98</v>
+        <v>-4.28</v>
       </c>
       <c r="F4" s="13">
         <v>-7.58</v>
@@ -1635,10 +1635,10 @@
         <v>0.5</v>
       </c>
       <c r="H4" s="13">
-        <v>2.6</v>
-      </c>
-      <c r="I4" s="8">
-        <v>5.2</v>
+        <v>3.3</v>
+      </c>
+      <c r="I4" s="12">
+        <v>6.6</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1666,7 +1666,7 @@
       <c r="H5" s="16">
         <v>8.8</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="12">
         <v>16</v>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       <c r="H6" s="19">
         <v>5.2</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="12">
         <v>14.18</v>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       <c r="H7" s="22">
         <v>4</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="12">
         <v>11.43</v>
       </c>
     </row>
@@ -1753,7 +1753,7 @@
       <c r="H8" s="25">
         <v>14.22</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="12">
         <v>9.81</v>
       </c>
     </row>
@@ -1774,16 +1774,16 @@
         <v>-39.8</v>
       </c>
       <c r="F9" s="28">
-        <v>-44.42</v>
+        <v>-44.41</v>
       </c>
       <c r="G9" s="28">
         <v>5.4</v>
       </c>
       <c r="H9" s="28">
-        <v>4.62</v>
+        <v>4.61</v>
       </c>
       <c r="I9" s="31">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1800,19 +1800,19 @@
         <v>8</v>
       </c>
       <c r="E10" s="34">
-        <v>-0.58</v>
+        <v>0</v>
       </c>
       <c r="F10" s="34">
-        <v>-44.42</v>
+        <v>-44.41</v>
       </c>
       <c r="G10" s="34">
         <v>9.2</v>
       </c>
       <c r="H10" s="34">
-        <v>43.84</v>
+        <v>44.41</v>
       </c>
       <c r="I10" s="34">
-        <v>4.77</v>
+        <v>4.83</v>
       </c>
     </row>
   </sheetData>
